--- a/tests/test_extract/testing_files/automation_filter.xlsx
+++ b/tests/test_extract/testing_files/automation_filter.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sparda\Desktop\Moseley Lab\Code\MESSES_main\MESSES\tests\test_extract\testing_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sparda\Desktop\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64612A16-59DA-4F51-A58D-FD2A0FC99C58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FEC5563-1D96-4005-B4B7-EB496F81C0C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{2B6F5095-5DFE-46EB-88DB-472A84D9538B}"/>
   </bookViews>
@@ -246,7 +246,7 @@
     <t>#filter=replicate:"s1"</t>
   </si>
   <si>
-    <t>#filter="replicate":"r'^s2$'"</t>
+    <t>#filter="replicate":r'^s2$'</t>
   </si>
 </sst>
 </file>
